--- a/Pruebas calificadas/COLEGIO VEINTE DE JULIO DIAGNÓSTICA 902_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO VEINTE DE JULIO DIAGNÓSTICA 902_CALIFICADO.xlsx
@@ -938,9 +938,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB2" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB2" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -1191,9 +1191,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB3" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB3" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -1440,9 +1440,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB4" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB4" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1693,9 +1693,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB5" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB5" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1946,9 +1946,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB6" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB6" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -2199,9 +2199,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB7" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB7" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -2705,9 +2705,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB9" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB9" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -2958,9 +2958,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB10" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB10" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -3464,9 +3464,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB12" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB12" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -3713,9 +3713,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB13" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB13" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -3966,9 +3966,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB14" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB14" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -4472,9 +4472,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB16" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB16" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -4725,9 +4725,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB17" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB17" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
@@ -5484,9 +5484,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB20" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB20" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -5737,9 +5737,9 @@
           <t>C</t>
         </is>
       </c>
-      <c r="AB21" s="4" t="inlineStr">
-        <is>
-          <t>INCORRECTO</t>
+      <c r="AB21" s="3" t="inlineStr">
+        <is>
+          <t>CORRECTO</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO VEINTE DE JULIO DIAGNÓSTICA 902_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO VEINTE DE JULIO DIAGNÓSTICA 902_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -819,7 +815,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1072,7 +1064,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1325,7 +1313,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1562,11 +1550,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1574,7 +1558,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1815,11 +1799,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -1827,7 +1807,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -2068,11 +2048,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2080,7 +2056,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -2321,11 +2297,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2333,7 +2305,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2574,11 +2546,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2586,7 +2554,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2827,11 +2795,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -2839,7 +2803,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3080,11 +3044,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3092,7 +3052,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3345,7 +3301,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3598,7 +3550,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3835,11 +3787,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -3847,7 +3795,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -4088,11 +4036,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4100,7 +4044,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -4341,11 +4285,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4353,7 +4293,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -4594,11 +4534,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4606,7 +4542,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4847,11 +4783,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -4859,7 +4791,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -5100,11 +5032,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5112,7 +5040,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -5353,11 +5281,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5365,7 +5289,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -5606,11 +5530,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5618,7 +5538,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -5859,11 +5779,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -5871,7 +5787,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -6112,11 +6028,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6124,7 +6036,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -6365,11 +6277,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6377,7 +6285,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -6618,11 +6526,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6630,7 +6534,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -6871,11 +6775,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -6883,7 +6783,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -7124,11 +7024,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7136,7 +7032,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -7377,11 +7273,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7389,7 +7281,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -7630,11 +7522,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7642,7 +7530,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -7883,11 +7771,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -7895,7 +7779,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -8136,11 +8020,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8148,7 +8028,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -8389,11 +8269,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8401,7 +8277,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -8644,11 +8520,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8656,7 +8528,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -8897,11 +8769,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -8909,7 +8777,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -9150,11 +9018,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -9162,7 +9026,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -9403,11 +9267,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -9415,7 +9275,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -9656,11 +9516,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -9668,7 +9524,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -9909,11 +9765,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -9921,7 +9773,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -10162,11 +10014,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -10174,7 +10022,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -10415,11 +10263,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -10427,7 +10271,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -10668,11 +10512,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001012033</t>
@@ -10680,7 +10520,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO VEINTE DE JULIO (IED)</t>
+          <t>COLEGIO VEINTE DE JULIO</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
